--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543_test.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543_test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.30-e03\content\data\output\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.26-e04\content\data\output\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE5FB7C-BECC-434B-9FFE-BB6CCFB829E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2D62D0-6B35-4F73-898F-AC09AC14C78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="669" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543_test.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543_test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.26-e04\content\data\output\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.28-e05\content\data\output\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2D62D0-6B35-4F73-898F-AC09AC14C78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7834931-62E0-44D2-A6FF-A57C0DCA5FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="669" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="303">
   <si>
     <t>CORE (COst REport) - AT</t>
   </si>
@@ -1114,7 +1114,7 @@
     <t>Sales Manager AT Test</t>
   </si>
   <si>
-    <t>E92010</t>
+    <t>E92012</t>
   </si>
   <si>
     <t>Susana Matarranz</t>
@@ -1124,6 +1124,9 @@
   </si>
   <si>
     <t>Jorge Puertas</t>
+  </si>
+  <si>
+    <t>E92013</t>
   </si>
   <si>
     <t>Sopore especializado</t>
@@ -16076,148 +16079,148 @@
         <v>91</v>
       </c>
       <c r="G7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="R7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="S7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="U7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="W7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="X7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Y7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Z7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AB7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AC7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AD7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AE7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AF7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AH7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AI7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AJ7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AK7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AP7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AR7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AS7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AT7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AU7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AV7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AW7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AX7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AY7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AZ7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BA7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BB7" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BC7" s="268"/>
       <c r="BD7" s="268"/>
@@ -16446,148 +16449,148 @@
         <v>91</v>
       </c>
       <c r="G9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="R9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="S9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="U9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="W9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="X9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Y9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Z9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AB9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AC9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AD9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AE9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AF9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AH9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AI9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AJ9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AK9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AP9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AR9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AS9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AT9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AU9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AV9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AW9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AX9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AY9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AZ9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BA9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BB9" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BC9" s="268"/>
       <c r="BD9" s="268"/>
@@ -16801,7 +16804,7 @@
     </row>
     <row r="11" spans="2:79" s="107" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C11" t="s">
         <v>101</v>
@@ -16810,154 +16813,154 @@
         <v>158</v>
       </c>
       <c r="E11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F11" s="288" t="s">
         <v>91</v>
       </c>
       <c r="G11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="R11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="S11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="U11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="W11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="X11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Y11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Z11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AB11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AC11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AD11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AE11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AF11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AH11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AI11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AJ11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AK11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AP11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AR11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AS11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AT11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AU11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AV11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AW11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AX11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AY11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AZ11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BA11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BB11" s="307" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BC11" s="268"/>
       <c r="BD11" s="268"/>
@@ -16986,7 +16989,7 @@
     </row>
     <row r="12" spans="2:79" s="107" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C12" t="s">
         <v>101</v>
@@ -16995,7 +16998,7 @@
         <v>158</v>
       </c>
       <c r="E12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F12" s="289" t="s">
         <v>92</v>
@@ -22201,7 +22204,7 @@
     </row>
     <row r="14" spans="2:80" s="107" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C14" t="s">
         <v>101</v>
@@ -22210,7 +22213,7 @@
         <v>158</v>
       </c>
       <c r="E14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F14"/>
       <c r="G14" s="290" t="s">
@@ -22387,7 +22390,7 @@
     </row>
     <row r="15" spans="2:80" s="107" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C15" t="s">
         <v>101</v>
@@ -22396,7 +22399,7 @@
         <v>158</v>
       </c>
       <c r="E15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F15"/>
       <c r="G15" s="291" t="s">

--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543_test.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543_test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.28-e05\content\data\output\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.29-e06\content\data\output\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7834931-62E0-44D2-A6FF-A57C0DCA5FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8842993-86BC-4D5B-84D6-6689584CFE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="669" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
